--- a/templates/deposit_template.xlsx
+++ b/templates/deposit_template.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12465"/>
+    <workbookView windowWidth="28800" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="投保机构存款归属表" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -502,15 +515,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="7">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -547,25 +560,54 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="仿宋_GB2312"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="9"/>
+      <sz val="12"/>
+      <name val="仿宋_GB2312"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color indexed="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color indexed="20"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="62"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="62"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -577,46 +619,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="42"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
-      <color indexed="62"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="53"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color indexed="62"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="62"/>
       <name val="宋体"/>
@@ -624,7 +627,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="60"/>
+      <color indexed="62"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -658,7 +661,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="62"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -670,55 +679,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="10"/>
+      <color indexed="60"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color indexed="42"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color indexed="56"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color indexed="23"/>
+      <color indexed="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="17"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color indexed="20"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -730,15 +723,35 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="56"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color indexed="56"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color indexed="56"/>
+      <sz val="12"/>
+      <color indexed="53"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -770,13 +783,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="62"/>
+        <fgColor indexed="47"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="36"/>
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -788,37 +831,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="51"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="10"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="49"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="11"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,13 +849,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="31"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="9"/>
+        <fgColor indexed="54"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -860,13 +867,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="55"/>
+        <fgColor indexed="53"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="45"/>
+        <fgColor indexed="31"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -878,25 +885,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="54"/>
+        <fgColor indexed="62"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="53"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="42"/>
+        <fgColor indexed="51"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="30"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="36"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1046,6 +1059,15 @@
       <right/>
       <top/>
       <bottom style="thick">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
         <color indexed="22"/>
       </bottom>
       <diagonal/>
@@ -1054,17 +1076,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thick">
+      <bottom style="medium">
         <color indexed="49"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="52"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1116,6 +1129,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="49"/>
       </top>
@@ -1128,8 +1150,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color indexed="30"/>
+      <bottom style="thick">
+        <color indexed="62"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1138,16 +1160,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="49"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="62"/>
+        <color indexed="30"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1165,617 +1178,617 @@
   </borders>
   <cellStyleXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1784,19 +1797,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1806,125 +1819,125 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1945,14 +1958,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1967,7 +1980,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1976,6 +1989,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1988,215 +2007,209 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="5" xfId="232" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="232" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="8" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="8" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="4" xfId="232" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="4" xfId="232" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="4" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="4" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="9" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="5" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="4" xfId="232" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="3" borderId="8" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="8" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="147" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="147" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="4" xfId="232" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="9" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="5" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="4" xfId="232" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="3" borderId="8" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="8" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="147" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="147" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="212" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="4" xfId="232" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="9" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="9" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="5" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="5" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="2" borderId="5" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="5" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="3" borderId="4" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="7" fillId="3" borderId="4" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="5" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="221" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="113" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="220" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2205,86 +2218,86 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="263">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="60% - 着色 2" xfId="3"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="4" builtinId="38"/>
-    <cellStyle name="输出 3" xfId="5"/>
-    <cellStyle name="20% - 强调文字颜色 1 2" xfId="6"/>
-    <cellStyle name="输入" xfId="7" builtinId="20"/>
-    <cellStyle name="千位分隔[0]" xfId="8" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="9" builtinId="39"/>
-    <cellStyle name="计算 2" xfId="10"/>
-    <cellStyle name="差" xfId="11" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="12" builtinId="3"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="13"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="14" builtinId="40"/>
-    <cellStyle name="超链接" xfId="15" builtinId="8"/>
-    <cellStyle name="百分比" xfId="16" builtinId="5"/>
-    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="17"/>
-    <cellStyle name="已访问的超链接" xfId="18" builtinId="9"/>
-    <cellStyle name="注释" xfId="19" builtinId="10"/>
-    <cellStyle name="常规 6" xfId="20"/>
-    <cellStyle name="60% - 强调文字颜色 2 3" xfId="21"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="22" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="23" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="24" builtinId="11"/>
-    <cellStyle name="标题" xfId="25" builtinId="15"/>
-    <cellStyle name="强调文字颜色 1 2 3" xfId="26"/>
-    <cellStyle name="常规 5 2" xfId="27"/>
-    <cellStyle name="60% - 强调文字颜色 2 2 2" xfId="28"/>
-    <cellStyle name="解释性文本" xfId="29" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="30" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="31" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="32" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="33" builtinId="18"/>
-    <cellStyle name="20% - 强调文字颜色 3 2 3" xfId="34"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="35" builtinId="44"/>
-    <cellStyle name="输出" xfId="36" builtinId="21"/>
-    <cellStyle name="计算" xfId="37" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="38" builtinId="23"/>
-    <cellStyle name="40% - 强调文字颜色 4 2" xfId="39"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="40" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="41" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="42" builtinId="24"/>
-    <cellStyle name="输出 2 3" xfId="43"/>
-    <cellStyle name="20% - 强调文字颜色 2 3" xfId="44"/>
-    <cellStyle name="汇总" xfId="45" builtinId="25"/>
-    <cellStyle name="60% - 强调文字颜色 4 2 3" xfId="46"/>
-    <cellStyle name="好" xfId="47" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 3 3" xfId="48"/>
-    <cellStyle name="着色 5" xfId="49"/>
-    <cellStyle name="适中" xfId="50" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="51" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="52" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="53" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="54" builtinId="31"/>
-    <cellStyle name="输出 2" xfId="55"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="56" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="57" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="58" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="59" builtinId="41"/>
-    <cellStyle name="输出 4" xfId="60"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="61" builtinId="42"/>
-    <cellStyle name="20% - 着色 1" xfId="62"/>
-    <cellStyle name="计算 3" xfId="63"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="64" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="65" builtinId="45"/>
-    <cellStyle name="20% - 着色 2" xfId="66"/>
-    <cellStyle name="计算 4" xfId="67"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="68" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="69" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="70" builtinId="49"/>
-    <cellStyle name="20% - 着色 3" xfId="71"/>
-    <cellStyle name="适中 2" xfId="72"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="73" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="74" builtinId="52"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="60% - 着色 2" xfId="49"/>
+    <cellStyle name="输出 3" xfId="50"/>
+    <cellStyle name="20% - 强调文字颜色 1 2" xfId="51"/>
+    <cellStyle name="计算 2" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 2" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2 2 2" xfId="54"/>
+    <cellStyle name="常规 6" xfId="55"/>
+    <cellStyle name="60% - 强调文字颜色 2 3" xfId="56"/>
+    <cellStyle name="强调文字颜色 1 2 3" xfId="57"/>
+    <cellStyle name="常规 5 2" xfId="58"/>
+    <cellStyle name="60% - 强调文字颜色 2 2 2" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 3 2 3" xfId="60"/>
+    <cellStyle name="40% - 强调文字颜色 4 2" xfId="61"/>
+    <cellStyle name="输出 2 3" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 2 3" xfId="63"/>
+    <cellStyle name="60% - 强调文字颜色 4 2 3" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 3 3" xfId="65"/>
+    <cellStyle name="着色 5" xfId="66"/>
+    <cellStyle name="输出 2" xfId="67"/>
+    <cellStyle name="输出 4" xfId="68"/>
+    <cellStyle name="20% - 着色 1" xfId="69"/>
+    <cellStyle name="计算 3" xfId="70"/>
+    <cellStyle name="20% - 着色 2" xfId="71"/>
+    <cellStyle name="计算 4" xfId="72"/>
+    <cellStyle name="20% - 着色 3" xfId="73"/>
+    <cellStyle name="适中 2" xfId="74"/>
     <cellStyle name="20% - 强调文字颜色 1 2 3" xfId="75"/>
     <cellStyle name="40% - 强调文字颜色 2 2" xfId="76"/>
     <cellStyle name="20% - 强调文字颜色 1 4" xfId="77"/>
@@ -3394,7 +3407,7 @@
       <c r="IS2" s="3"/>
       <c r="IT2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="14.25" spans="1:254">
+    <row r="3" s="1" customFormat="1" ht="17.6" spans="1:254">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -3408,9 +3421,9 @@
       <c r="G3" s="15"/>
       <c r="H3" s="16"/>
       <c r="I3" s="16"/>
-      <c r="J3" s="69"/>
+      <c r="J3" s="17"/>
       <c r="K3" s="16"/>
-      <c r="L3" s="70"/>
+      <c r="L3" s="18"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -3654,45 +3667,45 @@
       <c r="IS3"/>
       <c r="IT3"/>
     </row>
-    <row r="4" customFormat="1" ht="14.25" spans="1:11">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="1" ht="17.6" spans="1:254">
+      <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="22"/>
+      <c r="G4" s="24"/>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
       <c r="K4" s="16"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="28.5" customHeight="1" spans="1:254">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="25" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="3"/>
@@ -3944,29 +3957,29 @@
       <c r="IT5" s="3"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A6" s="27">
+      <c r="A6" s="29">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="31">
         <f>F6+F7+F10+F11</f>
         <v>0</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32">
+      <c r="E6" s="33"/>
+      <c r="F6" s="34">
         <f>F12-SUM(F13:F21)+F22</f>
         <v>0</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="71"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="37"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -4214,18 +4227,18 @@
       <c r="IT6" s="3"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A7" s="27"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="30" t="s">
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="32">
+      <c r="E7" s="33"/>
+      <c r="F7" s="34">
         <f>F23-SUM(F24:F31)+F32-F33+SUM(F34:F39)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H7"/>
@@ -4477,18 +4490,18 @@
       <c r="IT7" s="3"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A8" s="27"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="36" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32">
+      <c r="E8" s="33"/>
+      <c r="F8" s="34">
         <f>SUM(F40:F48)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H8"/>
@@ -4740,18 +4753,18 @@
       <c r="IT8" s="3"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="36" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32">
+      <c r="E9" s="33"/>
+      <c r="F9" s="34">
         <f>SUM(F49:F57)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H9"/>
@@ -5003,22 +5016,22 @@
       <c r="IT9" s="3"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="37" t="s">
+      <c r="A10" s="29"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32">
+      <c r="E10" s="33"/>
+      <c r="F10" s="34">
         <f>F58+F59</f>
         <v>0</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H10"/>
-      <c r="I10" s="72"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -5266,18 +5279,18 @@
       <c r="IT10" s="3"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A11" s="27"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="30" t="s">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32">
+      <c r="E11" s="33"/>
+      <c r="F11" s="34">
         <f>SUM(F62:F80)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H11"/>
@@ -5529,23 +5542,23 @@
       <c r="IT11" s="3"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A12" s="39">
+      <c r="A12" s="43">
         <v>2</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="33"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="35"/>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" s="3"/>
@@ -5795,19 +5808,19 @@
       <c r="IT12" s="3"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="31" t="s">
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="33"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="35"/>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" s="3"/>
@@ -6057,19 +6070,19 @@
       <c r="IT13" s="3"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="31" t="s">
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="33"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -6319,19 +6332,19 @@
       <c r="IT14" s="3"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="31" t="s">
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="33"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="35"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -6581,19 +6594,19 @@
       <c r="IT15" s="3"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="31" t="s">
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="33"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -6843,19 +6856,19 @@
       <c r="IT16" s="3"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="31" t="s">
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="33"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -7105,19 +7118,19 @@
       <c r="IT17" s="3"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="31" t="s">
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="33"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="35"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -7367,19 +7380,19 @@
       <c r="IT18" s="3"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A19" s="43"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="31" t="s">
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="33"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -7629,19 +7642,19 @@
       <c r="IT19" s="3"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="31" t="s">
+      <c r="A20" s="47"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="33"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -7891,19 +7904,19 @@
       <c r="IT20" s="3"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="46" t="s">
+      <c r="A21" s="47"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="42"/>
-      <c r="G21" s="49" t="s">
+      <c r="F21" s="46"/>
+      <c r="G21" s="53" t="s">
         <v>36</v>
       </c>
       <c r="H21" s="3"/>
@@ -8155,19 +8168,19 @@
       <c r="IT21" s="3"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="50" t="s">
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="52"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="56"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -8417,23 +8430,23 @@
       <c r="IT22" s="3"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A23" s="27">
+      <c r="A23" s="29">
         <v>3</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="E23" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="42"/>
-      <c r="G23" s="33"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -8683,19 +8696,19 @@
       <c r="IT23" s="3"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A24" s="27"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="31" t="s">
+      <c r="A24" s="29"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="42"/>
-      <c r="G24" s="31"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="33"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -8945,19 +8958,19 @@
       <c r="IT24" s="3"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A25" s="27"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="31" t="s">
+      <c r="A25" s="29"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="D25" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="42"/>
-      <c r="G25" s="31"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="33"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -9207,19 +9220,19 @@
       <c r="IT25" s="3"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A26" s="27"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="31" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="45" t="s">
+      <c r="D26" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="42"/>
-      <c r="G26" s="31"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="33"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -9469,19 +9482,19 @@
       <c r="IT26" s="3"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A27" s="27"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="31" t="s">
+      <c r="A27" s="29"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="E27" s="31" t="s">
+      <c r="E27" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="42"/>
-      <c r="G27" s="31"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="33"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -9731,19 +9744,19 @@
       <c r="IT27" s="3"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A28" s="27"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="31" t="s">
+      <c r="A28" s="29"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="D28" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="42"/>
-      <c r="G28" s="31"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="33"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -9993,19 +10006,19 @@
       <c r="IT28" s="3"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A29" s="27"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="31" t="s">
+      <c r="A29" s="29"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="D29" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="E29" s="31" t="s">
+      <c r="E29" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="42"/>
-      <c r="G29" s="31"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -10255,19 +10268,19 @@
       <c r="IT29" s="3"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A30" s="27"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="31" t="s">
+      <c r="A30" s="29"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="41" t="s">
+      <c r="D30" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="42"/>
-      <c r="G30" s="31"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -10517,19 +10530,19 @@
       <c r="IT30" s="3"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A31" s="27"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="46" t="s">
+      <c r="A31" s="29"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="F31" s="42"/>
-      <c r="G31" s="49" t="s">
+      <c r="F31" s="46"/>
+      <c r="G31" s="53" t="s">
         <v>36</v>
       </c>
       <c r="H31" s="3"/>
@@ -10781,19 +10794,19 @@
       <c r="IT31" s="3"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A32" s="27"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="31" t="s">
+      <c r="A32" s="29"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="41" t="s">
+      <c r="D32" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="31" t="s">
+      <c r="E32" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="42"/>
-      <c r="G32" s="31"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -11043,19 +11056,19 @@
       <c r="IT32" s="3"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A33" s="27"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="31" t="s">
+      <c r="A33" s="29"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="41" t="s">
+      <c r="D33" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="E33" s="31" t="s">
+      <c r="E33" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F33" s="42"/>
-      <c r="G33" s="31"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
@@ -11305,19 +11318,19 @@
       <c r="IT33" s="3"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A34" s="27"/>
-      <c r="B34" s="53"/>
-      <c r="C34" s="31" t="s">
+      <c r="A34" s="29"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D34" s="41" t="s">
+      <c r="D34" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="31" t="s">
+      <c r="E34" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F34" s="42"/>
-      <c r="G34" s="31"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -11567,19 +11580,19 @@
       <c r="IT34" s="3"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A35" s="27"/>
-      <c r="B35" s="53"/>
-      <c r="C35" s="31" t="s">
+      <c r="A35" s="29"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="41" t="s">
+      <c r="D35" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="E35" s="31" t="s">
+      <c r="E35" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="42"/>
-      <c r="G35" s="31"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -11829,19 +11842,19 @@
       <c r="IT35" s="3"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A36" s="27"/>
-      <c r="B36" s="53"/>
-      <c r="C36" s="31" t="s">
+      <c r="A36" s="29"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="D36" s="41" t="s">
+      <c r="D36" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="E36" s="31" t="s">
+      <c r="E36" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="42"/>
-      <c r="G36" s="31"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -12091,19 +12104,19 @@
       <c r="IT36" s="3"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A37" s="27"/>
-      <c r="B37" s="53"/>
-      <c r="C37" s="31" t="s">
+      <c r="A37" s="29"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="D37" s="41" t="s">
+      <c r="D37" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="31" t="s">
+      <c r="E37" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F37" s="42"/>
-      <c r="G37" s="31"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
@@ -12352,297 +12365,297 @@
       <c r="IS37" s="3"/>
       <c r="IT37" s="3"/>
     </row>
-    <row r="38" s="2" customFormat="1" ht="20" customHeight="1" spans="1:12">
-      <c r="A38" s="27"/>
-      <c r="B38" s="53"/>
-      <c r="C38" s="31" t="s">
+    <row r="38" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A38" s="29"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="D38" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E38" s="31" t="s">
+      <c r="E38" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F38" s="42"/>
-      <c r="G38" s="31"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="33"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" s="2" customFormat="1" ht="20" customHeight="1" spans="1:12">
-      <c r="A39" s="27"/>
-      <c r="B39" s="53"/>
-      <c r="C39" s="55" t="s">
+    <row r="39" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A39" s="29"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="56" t="s">
+      <c r="D39" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="31" t="s">
+      <c r="E39" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="42"/>
-      <c r="G39" s="33"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="35"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" s="2" customFormat="1" ht="20" customHeight="1" spans="1:10">
-      <c r="A40" s="57">
+    <row r="40" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A40" s="61">
         <v>4</v>
       </c>
-      <c r="B40" s="58" t="s">
+      <c r="B40" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="59" t="s">
+      <c r="C40" s="63" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="60" t="s">
+      <c r="D40" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="42"/>
-      <c r="G40" s="61"/>
-      <c r="J40" s="73"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="65"/>
+      <c r="J40" s="66"/>
     </row>
-    <row r="41" s="2" customFormat="1" ht="20" customHeight="1" spans="1:10">
-      <c r="A41" s="57"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="61" t="s">
+    <row r="41" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A41" s="61"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="58" t="s">
+      <c r="D41" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="E41" s="61" t="s">
+      <c r="E41" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="42"/>
-      <c r="G41" s="61"/>
-      <c r="J41" s="73"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="65"/>
+      <c r="J41" s="66"/>
     </row>
-    <row r="42" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A42" s="57"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="61" t="s">
+    <row r="42" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A42" s="61"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="58" t="s">
+      <c r="D42" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="61" t="s">
+      <c r="E42" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F42" s="42"/>
-      <c r="G42" s="61"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="65"/>
     </row>
-    <row r="43" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A43" s="57"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="61" t="s">
+    <row r="43" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A43" s="61"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="58" t="s">
+      <c r="D43" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="61" t="s">
+      <c r="E43" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="61"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="65"/>
     </row>
-    <row r="44" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A44" s="57"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="61" t="s">
+    <row r="44" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A44" s="61"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="58" t="s">
+      <c r="D44" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="61" t="s">
+      <c r="E44" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="42"/>
-      <c r="G44" s="61"/>
+      <c r="F44" s="46"/>
+      <c r="G44" s="65"/>
     </row>
-    <row r="45" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A45" s="57"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="61" t="s">
+    <row r="45" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A45" s="61"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="58" t="s">
+      <c r="D45" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="61" t="s">
+      <c r="E45" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="42"/>
-      <c r="G45" s="61"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="65"/>
     </row>
-    <row r="46" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A46" s="57"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="61" t="s">
+    <row r="46" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A46" s="61"/>
+      <c r="B46" s="62"/>
+      <c r="C46" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="58" t="s">
+      <c r="D46" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="E46" s="61" t="s">
+      <c r="E46" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="42"/>
-      <c r="G46" s="61"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="65"/>
     </row>
-    <row r="47" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A47" s="57"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="62" t="s">
+    <row r="47" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A47" s="61"/>
+      <c r="B47" s="62"/>
+      <c r="C47" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="63" t="s">
+      <c r="D47" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="62" t="s">
+      <c r="E47" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="42"/>
-      <c r="G47" s="49" t="s">
+      <c r="F47" s="46"/>
+      <c r="G47" s="53" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A48" s="57"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="31" t="s">
+    <row r="48" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A48" s="61"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="D48" s="41" t="s">
+      <c r="D48" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E48" s="31" t="s">
+      <c r="E48" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="42"/>
-      <c r="G48" s="31"/>
+      <c r="F48" s="46"/>
+      <c r="G48" s="33"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A49" s="57">
+    <row r="49" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A49" s="61">
         <v>5</v>
       </c>
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="D49" s="58" t="s">
+      <c r="D49" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="E49" s="61" t="s">
+      <c r="E49" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="42"/>
-      <c r="G49" s="61"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="65"/>
     </row>
-    <row r="50" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A50" s="57"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="61" t="s">
+    <row r="50" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A50" s="61"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="58" t="s">
+      <c r="D50" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="E50" s="61" t="s">
+      <c r="E50" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="42"/>
-      <c r="G50" s="61"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="65"/>
     </row>
-    <row r="51" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A51" s="57"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="61" t="s">
+    <row r="51" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A51" s="61"/>
+      <c r="B51" s="62"/>
+      <c r="C51" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="D51" s="58" t="s">
+      <c r="D51" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="E51" s="61" t="s">
+      <c r="E51" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F51" s="42"/>
-      <c r="G51" s="61"/>
+      <c r="F51" s="46"/>
+      <c r="G51" s="65"/>
     </row>
-    <row r="52" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A52" s="57"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="61" t="s">
+    <row r="52" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A52" s="61"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="58" t="s">
+      <c r="D52" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="E52" s="61" t="s">
+      <c r="E52" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="42"/>
-      <c r="G52" s="61"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="65"/>
     </row>
-    <row r="53" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A53" s="57"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="61" t="s">
+    <row r="53" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A53" s="61"/>
+      <c r="B53" s="62"/>
+      <c r="C53" s="65" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="58" t="s">
+      <c r="D53" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="E53" s="61" t="s">
+      <c r="E53" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F53" s="42"/>
-      <c r="G53" s="61"/>
+      <c r="F53" s="46"/>
+      <c r="G53" s="65"/>
     </row>
-    <row r="54" s="2" customFormat="1" ht="20" customHeight="1" spans="1:7">
-      <c r="A54" s="57"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="61" t="s">
+    <row r="54" s="2" customFormat="1" ht="20" customHeight="1" spans="1:254">
+      <c r="A54" s="61"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="58" t="s">
+      <c r="D54" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="61" t="s">
+      <c r="E54" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="42"/>
-      <c r="G54" s="61"/>
+      <c r="F54" s="46"/>
+      <c r="G54" s="65"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A55" s="57"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="61" t="s">
+      <c r="A55" s="61"/>
+      <c r="B55" s="62"/>
+      <c r="C55" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="D55" s="58" t="s">
+      <c r="D55" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="E55" s="61" t="s">
+      <c r="E55" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F55" s="42"/>
-      <c r="G55" s="61"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="65"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -12892,19 +12905,19 @@
       <c r="IT55" s="3"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A56" s="57"/>
-      <c r="B56" s="58"/>
-      <c r="C56" s="62" t="s">
+      <c r="A56" s="61"/>
+      <c r="B56" s="62"/>
+      <c r="C56" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="D56" s="63" t="s">
+      <c r="D56" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="E56" s="62" t="s">
+      <c r="E56" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="F56" s="42"/>
-      <c r="G56" s="49" t="s">
+      <c r="F56" s="46"/>
+      <c r="G56" s="53" t="s">
         <v>36</v>
       </c>
       <c r="H56" s="2"/>
@@ -13156,19 +13169,19 @@
       <c r="IT56" s="3"/>
     </row>
     <row r="57" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A57" s="57"/>
-      <c r="B57" s="58"/>
-      <c r="C57" s="31" t="s">
+      <c r="A57" s="61"/>
+      <c r="B57" s="62"/>
+      <c r="C57" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="D57" s="41" t="s">
+      <c r="D57" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="E57" s="31" t="s">
+      <c r="E57" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F57" s="42"/>
-      <c r="G57" s="31"/>
+      <c r="F57" s="46"/>
+      <c r="G57" s="33"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -13418,22 +13431,22 @@
       <c r="IT57" s="3"/>
     </row>
     <row r="58" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A58" s="39">
+      <c r="A58" s="43">
         <v>6</v>
       </c>
-      <c r="B58" s="64" t="s">
+      <c r="B58" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="C58" s="55"/>
-      <c r="D58" s="56" t="s">
+      <c r="C58" s="59"/>
+      <c r="D58" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="E58" s="65"/>
-      <c r="F58" s="32">
+      <c r="E58" s="70"/>
+      <c r="F58" s="34">
         <f>F60</f>
         <v>0</v>
       </c>
-      <c r="G58" s="33" t="s">
+      <c r="G58" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H58" s="3"/>
@@ -13685,18 +13698,18 @@
       <c r="IT58" s="3"/>
     </row>
     <row r="59" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A59" s="66"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="55"/>
-      <c r="D59" s="56" t="s">
+      <c r="A59" s="71"/>
+      <c r="B59" s="72"/>
+      <c r="C59" s="59"/>
+      <c r="D59" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="E59" s="65"/>
-      <c r="F59" s="32">
+      <c r="E59" s="70"/>
+      <c r="F59" s="34">
         <f>F61</f>
         <v>0</v>
       </c>
-      <c r="G59" s="33" t="s">
+      <c r="G59" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H59" s="3"/>
@@ -13948,23 +13961,23 @@
       <c r="IT59" s="3"/>
     </row>
     <row r="60" s="1" customFormat="1" ht="46" customHeight="1" spans="1:254">
-      <c r="A60" s="27">
+      <c r="A60" s="29">
         <v>7</v>
       </c>
-      <c r="B60" s="53" t="s">
+      <c r="B60" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="C60" s="31" t="s">
+      <c r="C60" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="D60" s="41" t="s">
+      <c r="D60" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="E60" s="31" t="s">
+      <c r="E60" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F60" s="42"/>
-      <c r="G60" s="31"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="33"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
@@ -14214,23 +14227,23 @@
       <c r="IT60" s="3"/>
     </row>
     <row r="61" s="1" customFormat="1" ht="42" customHeight="1" spans="1:254">
-      <c r="A61" s="27">
+      <c r="A61" s="29">
         <v>8</v>
       </c>
-      <c r="B61" s="53" t="s">
+      <c r="B61" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="C61" s="31" t="s">
+      <c r="C61" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="D61" s="41" t="s">
+      <c r="D61" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="E61" s="31" t="s">
+      <c r="E61" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F61" s="42"/>
-      <c r="G61" s="33"/>
+      <c r="F61" s="46"/>
+      <c r="G61" s="35"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
@@ -14480,23 +14493,23 @@
       <c r="IT61" s="3"/>
     </row>
     <row r="62" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A62" s="39">
+      <c r="A62" s="43">
         <v>9</v>
       </c>
-      <c r="B62" s="64" t="s">
+      <c r="B62" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="C62" s="31" t="s">
+      <c r="C62" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="D62" s="41" t="s">
+      <c r="D62" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="E62" s="31" t="s">
+      <c r="E62" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F62" s="42"/>
-      <c r="G62" s="31"/>
+      <c r="F62" s="46"/>
+      <c r="G62" s="33"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
@@ -14746,19 +14759,19 @@
       <c r="IT62" s="3"/>
     </row>
     <row r="63" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A63" s="43"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="31" t="s">
+      <c r="A63" s="47"/>
+      <c r="B63" s="73"/>
+      <c r="C63" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="41" t="s">
+      <c r="D63" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="E63" s="31" t="s">
+      <c r="E63" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="42"/>
-      <c r="G63" s="31"/>
+      <c r="F63" s="46"/>
+      <c r="G63" s="33"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
@@ -15008,19 +15021,19 @@
       <c r="IT63" s="3"/>
     </row>
     <row r="64" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A64" s="43"/>
-      <c r="B64" s="68"/>
-      <c r="C64" s="31" t="s">
+      <c r="A64" s="47"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="D64" s="41" t="s">
+      <c r="D64" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E64" s="31" t="s">
+      <c r="E64" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F64" s="42"/>
-      <c r="G64" s="31"/>
+      <c r="F64" s="46"/>
+      <c r="G64" s="33"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
@@ -15270,19 +15283,19 @@
       <c r="IT64" s="3"/>
     </row>
     <row r="65" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A65" s="43"/>
-      <c r="B65" s="68"/>
-      <c r="C65" s="31" t="s">
+      <c r="A65" s="47"/>
+      <c r="B65" s="73"/>
+      <c r="C65" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="D65" s="41" t="s">
+      <c r="D65" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="31" t="s">
+      <c r="E65" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F65" s="42"/>
-      <c r="G65" s="31"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="33"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
@@ -15532,19 +15545,19 @@
       <c r="IT65" s="3"/>
     </row>
     <row r="66" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A66" s="43"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="31" t="s">
+      <c r="A66" s="47"/>
+      <c r="B66" s="73"/>
+      <c r="C66" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="D66" s="41" t="s">
+      <c r="D66" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="E66" s="31" t="s">
+      <c r="E66" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F66" s="42"/>
-      <c r="G66" s="31"/>
+      <c r="F66" s="46"/>
+      <c r="G66" s="33"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
@@ -15794,19 +15807,19 @@
       <c r="IT66" s="3"/>
     </row>
     <row r="67" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A67" s="43"/>
-      <c r="B67" s="68"/>
-      <c r="C67" s="31" t="s">
+      <c r="A67" s="47"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="D67" s="41" t="s">
+      <c r="D67" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="E67" s="31" t="s">
+      <c r="E67" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="42"/>
-      <c r="G67" s="31"/>
+      <c r="F67" s="46"/>
+      <c r="G67" s="33"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
@@ -16056,19 +16069,19 @@
       <c r="IT67" s="3"/>
     </row>
     <row r="68" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A68" s="43"/>
-      <c r="B68" s="68"/>
-      <c r="C68" s="31" t="s">
+      <c r="A68" s="47"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="D68" s="41" t="s">
+      <c r="D68" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="E68" s="31" t="s">
+      <c r="E68" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="42"/>
-      <c r="G68" s="31"/>
+      <c r="F68" s="46"/>
+      <c r="G68" s="33"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
@@ -16318,19 +16331,19 @@
       <c r="IT68" s="3"/>
     </row>
     <row r="69" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A69" s="43"/>
-      <c r="B69" s="68"/>
-      <c r="C69" s="31" t="s">
+      <c r="A69" s="47"/>
+      <c r="B69" s="73"/>
+      <c r="C69" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="D69" s="41" t="s">
+      <c r="D69" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="E69" s="31" t="s">
+      <c r="E69" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="42"/>
-      <c r="G69" s="31"/>
+      <c r="F69" s="46"/>
+      <c r="G69" s="33"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
@@ -16580,19 +16593,19 @@
       <c r="IT69" s="3"/>
     </row>
     <row r="70" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A70" s="43"/>
-      <c r="B70" s="68"/>
-      <c r="C70" s="31" t="s">
+      <c r="A70" s="47"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="D70" s="41" t="s">
+      <c r="D70" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="E70" s="31" t="s">
+      <c r="E70" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F70" s="42"/>
-      <c r="G70" s="31"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="33"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
@@ -16842,19 +16855,19 @@
       <c r="IT70" s="3"/>
     </row>
     <row r="71" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A71" s="43"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="31" t="s">
+      <c r="A71" s="47"/>
+      <c r="B71" s="73"/>
+      <c r="C71" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="D71" s="41" t="s">
+      <c r="D71" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="E71" s="31" t="s">
+      <c r="E71" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="42"/>
-      <c r="G71" s="31"/>
+      <c r="F71" s="46"/>
+      <c r="G71" s="33"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
@@ -17104,19 +17117,19 @@
       <c r="IT71" s="3"/>
     </row>
     <row r="72" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A72" s="43"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="31" t="s">
+      <c r="A72" s="47"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="D72" s="41" t="s">
+      <c r="D72" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E72" s="31" t="s">
+      <c r="E72" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F72" s="42"/>
-      <c r="G72" s="31"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="33"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
@@ -17366,19 +17379,19 @@
       <c r="IT72" s="3"/>
     </row>
     <row r="73" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A73" s="43"/>
-      <c r="B73" s="68"/>
-      <c r="C73" s="31" t="s">
+      <c r="A73" s="47"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="D73" s="41" t="s">
+      <c r="D73" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="E73" s="31" t="s">
+      <c r="E73" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F73" s="42"/>
-      <c r="G73" s="31"/>
+      <c r="F73" s="46"/>
+      <c r="G73" s="33"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
@@ -17628,19 +17641,19 @@
       <c r="IT73" s="3"/>
     </row>
     <row r="74" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A74" s="43"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="31" t="s">
+      <c r="A74" s="47"/>
+      <c r="B74" s="73"/>
+      <c r="C74" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="D74" s="41" t="s">
+      <c r="D74" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="E74" s="31" t="s">
+      <c r="E74" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F74" s="42"/>
-      <c r="G74" s="31"/>
+      <c r="F74" s="46"/>
+      <c r="G74" s="33"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
@@ -17890,19 +17903,19 @@
       <c r="IT74" s="3"/>
     </row>
     <row r="75" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A75" s="43"/>
-      <c r="B75" s="68"/>
-      <c r="C75" s="31" t="s">
+      <c r="A75" s="47"/>
+      <c r="B75" s="73"/>
+      <c r="C75" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="D75" s="41" t="s">
+      <c r="D75" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="E75" s="31" t="s">
+      <c r="E75" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F75" s="42"/>
-      <c r="G75" s="31"/>
+      <c r="F75" s="46"/>
+      <c r="G75" s="33"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
@@ -18152,19 +18165,19 @@
       <c r="IT75" s="3"/>
     </row>
     <row r="76" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A76" s="43"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="31" t="s">
+      <c r="A76" s="47"/>
+      <c r="B76" s="73"/>
+      <c r="C76" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="D76" s="41" t="s">
+      <c r="D76" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="E76" s="31" t="s">
+      <c r="E76" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F76" s="42"/>
-      <c r="G76" s="31"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="33"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -18414,19 +18427,19 @@
       <c r="IT76" s="3"/>
     </row>
     <row r="77" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A77" s="43"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="31" t="s">
+      <c r="A77" s="47"/>
+      <c r="B77" s="73"/>
+      <c r="C77" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D77" s="41" t="s">
+      <c r="D77" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="E77" s="31" t="s">
+      <c r="E77" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F77" s="42"/>
-      <c r="G77" s="31"/>
+      <c r="F77" s="46"/>
+      <c r="G77" s="33"/>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
@@ -18676,8 +18689,8 @@
       <c r="IT77" s="3"/>
     </row>
     <row r="78" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A78" s="43"/>
-      <c r="B78" s="68"/>
+      <c r="A78" s="47"/>
+      <c r="B78" s="73"/>
       <c r="C78" s="74" t="s">
         <v>143</v>
       </c>
@@ -18687,7 +18700,7 @@
       <c r="E78" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F78" s="42"/>
+      <c r="F78" s="46"/>
       <c r="G78" s="74"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
@@ -18938,8 +18951,8 @@
       <c r="IT78" s="3"/>
     </row>
     <row r="79" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A79" s="43"/>
-      <c r="B79" s="68"/>
+      <c r="A79" s="47"/>
+      <c r="B79" s="73"/>
       <c r="C79" s="74" t="s">
         <v>145</v>
       </c>
@@ -18949,7 +18962,7 @@
       <c r="E79" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F79" s="42"/>
+      <c r="F79" s="46"/>
       <c r="G79" s="74"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
@@ -19211,7 +19224,7 @@
       <c r="E80" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F80" s="42"/>
+      <c r="F80" s="46"/>
       <c r="G80" s="74"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
@@ -19462,10 +19475,10 @@
       <c r="IT80" s="3"/>
     </row>
     <row r="81" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A81" s="39">
+      <c r="A81" s="43">
         <v>10</v>
       </c>
-      <c r="B81" s="64" t="s">
+      <c r="B81" s="69" t="s">
         <v>149</v>
       </c>
       <c r="C81" s="78">
@@ -19475,8 +19488,8 @@
       <c r="D81" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="23"/>
-      <c r="F81" s="32">
+      <c r="E81" s="25"/>
+      <c r="F81" s="34">
         <f>SUM(F84:F93)</f>
         <v>0</v>
       </c>
@@ -19735,15 +19748,15 @@
       <c r="A82" s="81"/>
       <c r="B82" s="82"/>
       <c r="C82" s="78"/>
-      <c r="D82" s="41" t="s">
+      <c r="D82" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="E82" s="31"/>
-      <c r="F82" s="32">
+      <c r="E82" s="33"/>
+      <c r="F82" s="34">
         <f>SUM(F94:F103)</f>
         <v>0</v>
       </c>
-      <c r="G82" s="33" t="s">
+      <c r="G82" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H82" s="3"/>
@@ -19998,15 +20011,15 @@
       <c r="A83" s="81"/>
       <c r="B83" s="82"/>
       <c r="C83" s="83"/>
-      <c r="D83" s="53" t="s">
+      <c r="D83" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="E83" s="31"/>
-      <c r="F83" s="32">
+      <c r="E83" s="33"/>
+      <c r="F83" s="34">
         <f>SUM(F104:F106)</f>
         <v>0</v>
       </c>
-      <c r="G83" s="33" t="s">
+      <c r="G83" s="35" t="s">
         <v>15</v>
       </c>
       <c r="H83" s="3"/>
@@ -20258,23 +20271,23 @@
       <c r="IT83" s="3"/>
     </row>
     <row r="84" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A84" s="39">
+      <c r="A84" s="43">
         <v>11</v>
       </c>
       <c r="B84" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="31" t="s">
+      <c r="C84" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D84" s="45" t="s">
+      <c r="D84" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E84" s="31" t="s">
+      <c r="E84" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F84" s="42"/>
-      <c r="G84" s="31"/>
+      <c r="F84" s="46"/>
+      <c r="G84" s="33"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
@@ -20524,19 +20537,19 @@
       <c r="IT84" s="3"/>
     </row>
     <row r="85" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A85" s="39"/>
+      <c r="A85" s="43"/>
       <c r="B85" s="84"/>
-      <c r="C85" s="31" t="s">
+      <c r="C85" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D85" s="45" t="s">
+      <c r="D85" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E85" s="31" t="s">
+      <c r="E85" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F85" s="42"/>
-      <c r="G85" s="31"/>
+      <c r="F85" s="46"/>
+      <c r="G85" s="33"/>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
@@ -20786,19 +20799,19 @@
       <c r="IT85" s="3"/>
     </row>
     <row r="86" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A86" s="39"/>
+      <c r="A86" s="43"/>
       <c r="B86" s="84"/>
-      <c r="C86" s="31" t="s">
+      <c r="C86" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D86" s="45" t="s">
+      <c r="D86" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E86" s="31" t="s">
+      <c r="E86" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F86" s="42"/>
-      <c r="G86" s="31"/>
+      <c r="F86" s="46"/>
+      <c r="G86" s="33"/>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
@@ -21048,19 +21061,19 @@
       <c r="IT86" s="3"/>
     </row>
     <row r="87" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A87" s="39"/>
+      <c r="A87" s="43"/>
       <c r="B87" s="84"/>
-      <c r="C87" s="31" t="s">
+      <c r="C87" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D87" s="45" t="s">
+      <c r="D87" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E87" s="31" t="s">
+      <c r="E87" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F87" s="42"/>
-      <c r="G87" s="31"/>
+      <c r="F87" s="46"/>
+      <c r="G87" s="33"/>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
@@ -21310,19 +21323,19 @@
       <c r="IT87" s="3"/>
     </row>
     <row r="88" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A88" s="39"/>
+      <c r="A88" s="43"/>
       <c r="B88" s="84"/>
-      <c r="C88" s="31" t="s">
+      <c r="C88" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="D88" s="45" t="s">
+      <c r="D88" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E88" s="31" t="s">
+      <c r="E88" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F88" s="42"/>
-      <c r="G88" s="31"/>
+      <c r="F88" s="46"/>
+      <c r="G88" s="33"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
@@ -21572,19 +21585,19 @@
       <c r="IT88" s="3"/>
     </row>
     <row r="89" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A89" s="39"/>
+      <c r="A89" s="43"/>
       <c r="B89" s="84"/>
-      <c r="C89" s="31" t="s">
+      <c r="C89" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D89" s="45" t="s">
+      <c r="D89" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E89" s="31" t="s">
+      <c r="E89" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F89" s="42"/>
-      <c r="G89" s="31"/>
+      <c r="F89" s="46"/>
+      <c r="G89" s="33"/>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
@@ -21834,19 +21847,19 @@
       <c r="IT89" s="3"/>
     </row>
     <row r="90" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A90" s="39"/>
+      <c r="A90" s="43"/>
       <c r="B90" s="84"/>
-      <c r="C90" s="31" t="s">
+      <c r="C90" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D90" s="41" t="s">
+      <c r="D90" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E90" s="31" t="s">
+      <c r="E90" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F90" s="42"/>
-      <c r="G90" s="31"/>
+      <c r="F90" s="46"/>
+      <c r="G90" s="33"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
@@ -22096,19 +22109,19 @@
       <c r="IT90" s="3"/>
     </row>
     <row r="91" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A91" s="39"/>
+      <c r="A91" s="43"/>
       <c r="B91" s="84"/>
-      <c r="C91" s="31" t="s">
+      <c r="C91" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D91" s="41" t="s">
+      <c r="D91" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E91" s="31" t="s">
+      <c r="E91" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F91" s="42"/>
-      <c r="G91" s="50"/>
+      <c r="F91" s="46"/>
+      <c r="G91" s="54"/>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
@@ -22358,18 +22371,18 @@
       <c r="IT91" s="3"/>
     </row>
     <row r="92" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A92" s="39"/>
+      <c r="A92" s="43"/>
       <c r="B92" s="84"/>
-      <c r="C92" s="46" t="s">
+      <c r="C92" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="D92" s="54" t="s">
+      <c r="D92" s="58" t="s">
         <v>26</v>
       </c>
       <c r="E92" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="F92" s="42"/>
+      <c r="F92" s="46"/>
       <c r="G92" s="86" t="s">
         <v>36</v>
       </c>
@@ -22622,18 +22635,18 @@
       <c r="IT92" s="3"/>
     </row>
     <row r="93" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A93" s="39"/>
+      <c r="A93" s="43"/>
       <c r="B93" s="84"/>
-      <c r="C93" s="46" t="s">
+      <c r="C93" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="D93" s="54" t="s">
+      <c r="D93" s="58" t="s">
         <v>152</v>
       </c>
       <c r="E93" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="F93" s="42"/>
+      <c r="F93" s="46"/>
       <c r="G93" s="86" t="s">
         <v>36</v>
       </c>
@@ -22886,23 +22899,23 @@
       <c r="IT93" s="3"/>
     </row>
     <row r="94" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A94" s="39">
+      <c r="A94" s="43">
         <v>12</v>
       </c>
-      <c r="B94" s="64" t="s">
+      <c r="B94" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="C94" s="23" t="s">
+      <c r="C94" s="25" t="s">
         <v>42</v>
       </c>
       <c r="D94" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="E94" s="24" t="s">
+      <c r="E94" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F94" s="42"/>
-      <c r="G94" s="31"/>
+      <c r="F94" s="46"/>
+      <c r="G94" s="33"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
@@ -23154,17 +23167,17 @@
     <row r="95" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
       <c r="A95" s="81"/>
       <c r="B95" s="82"/>
-      <c r="C95" s="31" t="s">
+      <c r="C95" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D95" s="45" t="s">
+      <c r="D95" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="E95" s="31" t="s">
+      <c r="E95" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F95" s="42"/>
-      <c r="G95" s="23"/>
+      <c r="F95" s="46"/>
+      <c r="G95" s="25"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
@@ -23416,17 +23429,17 @@
     <row r="96" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
       <c r="A96" s="81"/>
       <c r="B96" s="82"/>
-      <c r="C96" s="31" t="s">
+      <c r="C96" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="D96" s="45" t="s">
+      <c r="D96" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="E96" s="31" t="s">
+      <c r="E96" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F96" s="42"/>
-      <c r="G96" s="31"/>
+      <c r="F96" s="46"/>
+      <c r="G96" s="33"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
@@ -23678,17 +23691,17 @@
     <row r="97" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
       <c r="A97" s="81"/>
       <c r="B97" s="82"/>
-      <c r="C97" s="31" t="s">
+      <c r="C97" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="D97" s="45" t="s">
+      <c r="D97" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="E97" s="31" t="s">
+      <c r="E97" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F97" s="42"/>
-      <c r="G97" s="31"/>
+      <c r="F97" s="46"/>
+      <c r="G97" s="33"/>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
@@ -23940,17 +23953,17 @@
     <row r="98" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
       <c r="A98" s="81"/>
       <c r="B98" s="82"/>
-      <c r="C98" s="31" t="s">
+      <c r="C98" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="D98" s="45" t="s">
+      <c r="D98" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="E98" s="31" t="s">
+      <c r="E98" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F98" s="42"/>
-      <c r="G98" s="31"/>
+      <c r="F98" s="46"/>
+      <c r="G98" s="33"/>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
@@ -24202,17 +24215,17 @@
     <row r="99" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
       <c r="A99" s="81"/>
       <c r="B99" s="82"/>
-      <c r="C99" s="31" t="s">
+      <c r="C99" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D99" s="45" t="s">
+      <c r="D99" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="E99" s="31" t="s">
+      <c r="E99" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F99" s="42"/>
-      <c r="G99" s="31"/>
+      <c r="F99" s="46"/>
+      <c r="G99" s="33"/>
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
@@ -24464,17 +24477,17 @@
     <row r="100" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
       <c r="A100" s="81"/>
       <c r="B100" s="82"/>
-      <c r="C100" s="31" t="s">
+      <c r="C100" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D100" s="45" t="s">
+      <c r="D100" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="E100" s="31" t="s">
+      <c r="E100" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F100" s="42"/>
-      <c r="G100" s="31"/>
+      <c r="F100" s="46"/>
+      <c r="G100" s="33"/>
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
@@ -24726,16 +24739,16 @@
     <row r="101" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
       <c r="A101" s="81"/>
       <c r="B101" s="82"/>
-      <c r="C101" s="46" t="s">
+      <c r="C101" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="D101" s="47" t="s">
+      <c r="D101" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="E101" s="46" t="s">
+      <c r="E101" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F101" s="42"/>
+      <c r="F101" s="46"/>
       <c r="G101" s="86" t="s">
         <v>36</v>
       </c>
@@ -24990,17 +25003,17 @@
     <row r="102" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
       <c r="A102" s="81"/>
       <c r="B102" s="82"/>
-      <c r="C102" s="31" t="s">
+      <c r="C102" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D102" s="45" t="s">
+      <c r="D102" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="E102" s="31" t="s">
+      <c r="E102" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F102" s="42"/>
-      <c r="G102" s="31"/>
+      <c r="F102" s="46"/>
+      <c r="G102" s="33"/>
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
@@ -25250,18 +25263,18 @@
       <c r="IT102" s="3"/>
     </row>
     <row r="103" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A103" s="66"/>
+      <c r="A103" s="71"/>
       <c r="B103" s="88"/>
-      <c r="C103" s="46" t="s">
+      <c r="C103" s="50" t="s">
         <v>153</v>
       </c>
       <c r="D103" s="89" t="s">
         <v>154</v>
       </c>
-      <c r="E103" s="46" t="s">
+      <c r="E103" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F103" s="42"/>
+      <c r="F103" s="46"/>
       <c r="G103" s="86" t="s">
         <v>36</v>
       </c>
@@ -25517,7 +25530,7 @@
       <c r="A104" s="81">
         <v>13</v>
       </c>
-      <c r="B104" s="64" t="s">
+      <c r="B104" s="69" t="s">
         <v>155</v>
       </c>
       <c r="C104" s="90" t="s">
@@ -25526,11 +25539,11 @@
       <c r="D104" s="79" t="s">
         <v>157</v>
       </c>
-      <c r="E104" s="23" t="s">
+      <c r="E104" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="F104" s="42"/>
-      <c r="G104" s="31"/>
+      <c r="F104" s="46"/>
+      <c r="G104" s="33"/>
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
@@ -25785,14 +25798,14 @@
       <c r="C105" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="D105" s="41" t="s">
+      <c r="D105" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="E105" s="31" t="s">
+      <c r="E105" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F105" s="42"/>
-      <c r="G105" s="31"/>
+      <c r="F105" s="46"/>
+      <c r="G105" s="33"/>
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
@@ -26042,8 +26055,8 @@
       <c r="IT105" s="3"/>
     </row>
     <row r="106" s="1" customFormat="1" ht="20" customHeight="1" spans="1:254">
-      <c r="A106" s="66"/>
-      <c r="B106" s="67"/>
+      <c r="A106" s="71"/>
+      <c r="B106" s="72"/>
       <c r="C106" s="74" t="s">
         <v>159</v>
       </c>
@@ -26053,7 +26066,7 @@
       <c r="E106" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F106" s="42"/>
+      <c r="F106" s="46"/>
       <c r="G106" s="74"/>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
